--- a/planering/kemi-planering.xlsx
+++ b/planering/kemi-planering.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Täckning" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Moment'!$A$1:$K$117</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Delområden'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Områden'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Moment'!$A$1:$K$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Delområden'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Områden'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Labbar'!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Täckning'!$A$1:$C$24</definedName>
   </definedNames>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5786,21 +5786,21 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Material, produkter och hållbarhet</t>
+          <t>Repetition inför nationella proven</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Repetition inför nationella proven</t>
+          <t>Materia, atomer och föreningar</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Begrepp och modeller: repetition</t>
+          <t>Partikelmodellen och separation: repetition</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Partikel, atom, grundämne, molekyl, jon, reaktion; vilka modeller som används var.</t>
+          <t>Ämnen och blandningar, aggregationsformer, separations- och analysmetoder.</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>partikelmodell, atom, reaktionsformel, kretslopp</t>
+          <t>partikelmodell, blandning, filtrering, destillation</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -5841,21 +5841,21 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Material, produkter och hållbarhet</t>
+          <t>Repetition inför nationella proven</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Repetition inför nationella proven</t>
+          <t>Materia, atomer och föreningar</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -5865,52 +5865,52 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Undersökningar och information: repetition</t>
+          <t>Atomer och periodiska systemet: repetition</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Planera, genomföra och värdera en undersökning; granska källor; läsa tabeller och diagram.</t>
+          <t>Atomens byggnad, grundämnen och periodiska systemet; jonbildning.</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>variabel, felkälla, källa, slutsats</t>
+          <t>atom, elektron, grundämne, period, grupp, jon</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande; Egna systematiska undersökningar: påståenden kan prövas och kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Använda kemins begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>Observationer och experiment (analoga och digitala verktyg): undersökningsbara frågor, planering, utförande, värdering och dokumentation; Informationssökning, kritisk granskning och användning av information som rör kemi</t>
+          <t>Materiens uppbyggnad, kretslopp och oförstörbarhet med partikelmodeller; grundämnen, molekyl- och jonföreningar, kemiska reaktioner; atomer, elektroner och kärnpartiklar</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Systematiska undersökningar</t>
+          <t>Begrepp och förklaringsmodeller</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Material, produkter och hållbarhet</t>
+          <t>Repetition inför nationella proven</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Repetition inför nationella proven</t>
+          <t>Materia, atomer och föreningar</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -5920,52 +5920,52 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Resonera om miljö och hälsa: repetition</t>
+          <t>Föreningar och reaktioner: repetition</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>Övningar i att argumentera med belägg och motargument i frågor om miljö och hälsa.</t>
+          <t>Molekyler och joner, reaktionsformler och massans oförstörbarhet.</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>argument, belägg, nyans</t>
+          <t>molekyl, jonförening, reaktionsformel, oförstörbarhet</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>Formulera egna och granska andras argument; kommunicera; hantera praktiska och etiska valsituationer om miljö och hälsa</t>
+          <t>Använda kemins begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>Argumentation och ställningstaganden i aktuella frågor som rör miljö och hälsa; Kemiska processer i mark, luft och vatten och koppling till miljö och hälsa: växthuseffekten, vattenrening, miljögifter; Några produkters livscykler och påverkan på miljön</t>
+          <t>Materiens uppbyggnad, kretslopp och oförstörbarhet med partikelmodeller; grundämnen, molekyl- och jonföreningar, kemiska reaktioner; atomer, elektroner och kärnpartiklar</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Granska information, kommunicera och ta ställning</t>
+          <t>Begrepp och förklaringsmodeller</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Material, produkter och hållbarhet</t>
+          <t>Repetition inför nationella proven</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Repetition inför nationella proven</t>
+          <t>Materia, atomer och föreningar</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5984,8 +5984,478 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Materia, atomer och föreningar</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Om tid / fördjupning</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Begreppskartor</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Vatten, miljö och livets kemi</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Lektionsmoment</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Vatten, syror och baser: repetition</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Lösningsmedel, pH och neutralisation.</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>lösning, pH, syra, bas, neutralisation</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>Använda kemins begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>Separations- och analysmetoder, t.ex. filtrering, fällning, pH-mätning och identifikation av ämnen; Vatten som lösningsmedel och transportör av ämnen, t.ex. i mark, växter och människokroppen</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Begrepp och förklaringsmodeller</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Vatten, miljö och livets kemi</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Lektionsmoment</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Miljö och kretslopp: repetition</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Luft, växthuseffekt, vatten och miljögifter; kolets kretslopp.</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>växthuseffekt, miljögift, kolets kretslopp</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Kunskaper om kemin i naturen, i samhället och i människokroppen</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>Kemiska processer i mark, luft och vatten och koppling till miljö och hälsa: växthuseffekten, vattenrening, miljögifter; Kolatomens egenskaper och kretslopp i naturen, i samhället och i människokroppen</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>Begrepp och förklaringsmodeller</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Vatten, miljö och livets kemi</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Lektionsmoment</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Livets kemi: repetition</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>Kolhydrater, proteiner och fetter; material och livscykler.</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>kolhydrat, protein, fett, livscykel</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>Kunskaper om kemin i naturen, i samhället och i människokroppen</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>Kolhydrater, proteiner och fetter och deras funktioner i människokroppen; Utveckling av produkter och material, t.ex. läkemedel, funktionskläder och batterier; Några produkters livscykler och påverkan på miljön</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Begrepp och förklaringsmodeller</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Vatten, miljö och livets kemi</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Om tid / fördjupning</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>Gamla nationella prov</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" s="4" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Undersökningar, källor och argument</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Lektionsmoment</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Planera och värdera undersökningar</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>Variabler, rättvist försök, mätfel; läsa tabeller och diagram.</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>variabel, felkälla, tabell, diagram, slutsats</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>Egna systematiska undersökningar: påståenden kan prövas och kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>Observationer och experiment (analoga och digitala verktyg): undersökningsbara frågor, planering, utförande, värdering och dokumentation</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Systematiska undersökningar</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Undersökningar, källor och argument</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Lektionsmoment</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Granska information</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Källor, avsändare och syfte; kemipåståenden i reklam.</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>källa, trovärdighet, påstående</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Informationssökning, kritisk granskning och användning av information som rör kemi</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>Granska information, kommunicera och ta ställning</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Undersökningar, källor och argument</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Lektionsmoment</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Resonera om miljö och hälsa: repetition</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>Argumentera med belägg och motargument i frågor om miljö och hälsa.</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>argument, belägg, nyans</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>Formulera egna och granska andras argument; kommunicera; hantera praktiska och etiska valsituationer om miljö och hälsa</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>Argumentation och ställningstaganden i aktuella frågor som rör miljö och hälsa; Kemiska processer i mark, luft och vatten och koppling till miljö och hälsa: växthuseffekten, vattenrening, miljögifter; Några produkters livscykler och påverkan på miljön</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Granska information, kommunicera och ta ställning</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Undersökningar, källor och argument</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Om tid / fördjupning</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Gamla nationella prov</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Undersökningar, källor och argument</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Om tid / fördjupning</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Provstrategier</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K117"/>
+  <autoFilter ref="A1:K127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5996,7 +6466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6693,46 +7163,126 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Material, produkter och hållbarhet</t>
+          <t>Repetition inför nationella proven</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
+          <t>Materia, atomer och föreningar</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Eleven kan koppla ihop partikelmodell, atombyggnad, periodiska systemet, molekyler och joner i nya sammanhang.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>E: visar grundläggande kunskaper. C: visar goda kunskaper och drar slutsatser. A: använder flera modeller i nya situationer och motiverar.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Modeller genom hela kursen</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Gamla nationella prov; Begreppskartor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Repetition inför nationella proven</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Eleven kan koppla ihop kemins delar och visa sina kunskaper i den form som nationella proven prövar.</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Vatten, miljö och livets kemi</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Eleven kan koppla ihop vatten, syror och baser, miljökemi, kolföreningar och livets kemi i nya sammanhang.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>E: visar grundläggande kunskaper. C: förklarar samband och drar slutsatser. A: resonerar med flera förklaringsmodeller.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Modeller genom hela kursen</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Gamla nationella prov</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Undersökningar, källor och argument</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Eleven kan genomföra och värdera undersökningar, granska information och argumentera i frågor om miljö och hälsa.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>E: visar grundläggande kunskaper. C: visar goda kunskaper och drar slutsatser. A: genomför egna resonemang med välutvecklade belägg i frågor om miljö och hälsa.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Modeller genom hela kursen</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Gamla nationella prov</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Gamla nationella prov; Provstrategier</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6743,7 +7293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6915,11 +7465,29 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Repetition inför nationella proven</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Binder ihop kemins begrepp och modeller, undersökningar och argumentation inför de nationella proven.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7549,7 +8117,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -7564,7 +8132,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -7654,7 +8222,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -7669,7 +8237,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -7684,7 +8252,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -7699,7 +8267,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -7714,7 +8282,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -7729,7 +8297,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -7744,7 +8312,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -7759,7 +8327,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -7834,7 +8402,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -7849,7 +8417,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
